--- a/output/admin-reporting/large-payments.xlsx
+++ b/output/admin-reporting/large-payments.xlsx
@@ -52373,7 +52373,7 @@
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -52443,7 +52443,7 @@
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -52513,7 +52513,7 @@
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -52583,7 +52583,7 @@
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -52653,7 +52653,7 @@
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -52723,7 +52723,7 @@
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -52793,7 +52793,7 @@
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -52863,7 +52863,7 @@
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -52933,7 +52933,7 @@
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53003,7 +53003,7 @@
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53073,7 +53073,7 @@
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53143,7 +53143,7 @@
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53213,7 +53213,7 @@
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53283,7 +53283,7 @@
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53353,7 +53353,7 @@
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53423,7 +53423,7 @@
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53493,7 +53493,7 @@
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53563,7 +53563,7 @@
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53633,7 +53633,7 @@
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53703,7 +53703,7 @@
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53773,7 +53773,7 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53843,7 +53843,7 @@
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53913,7 +53913,7 @@
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -53983,7 +53983,7 @@
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -54053,7 +54053,7 @@
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -54123,7 +54123,7 @@
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -54193,7 +54193,7 @@
       </c>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -54263,7 +54263,7 @@
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -54593,7 +54593,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
